--- a/docs/downloads/经营分_鲁西省区__济南北片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_鲁西省区__济南北片区_2026-10-18.xlsx
@@ -863,29 +863,29 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>6859701646813972493</t>
+          <t>7395777577689810953</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>希岸酒店（济南站济南动物园店）</t>
+          <t>希岸轻雅酒店（济南济阳不夜城济北公园店）</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>希岸酒店(济南泺口动物园店)</t>
+          <t>希岸轻雅酒店(济南济阳不夜城济北公园店)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="I4" t="n">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>10</v>
       </c>
       <c r="M4" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="N4" t="n">
         <v>30</v>
@@ -911,7 +911,7 @@
         <v>30</v>
       </c>
       <c r="Q4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="R4" t="n">
         <v>30</v>
@@ -951,29 +951,29 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>7395777577689810953</t>
+          <t>6859701646813972493</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>希岸轻雅酒店（济南济阳不夜城济北公园店）</t>
+          <t>希岸酒店（济南站济南动物园店）</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>希岸轻雅酒店(济南济阳不夜城济北公园店)</t>
+          <t>希岸酒店(济南泺口动物园店)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H5" t="n">
         <v>90</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -987,7 +987,7 @@
         <v>10</v>
       </c>
       <c r="M5" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="N5" t="n">
         <v>30</v>
@@ -999,7 +999,7 @@
         <v>30</v>
       </c>
       <c r="Q5" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="R5" t="n">
         <v>30</v>
@@ -1501,7 +1501,7 @@
         <v>92</v>
       </c>
       <c r="I11" t="n">
-        <v>-8</v>
+        <v>0</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1831,17 +1831,17 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>7058846272626624519</t>
+          <t>7114640050347837473</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0济南黄台环球家居店）</t>
+          <t>维也纳国际酒店（5.0版济南泉城欧乐堡传化店）</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>维也纳酒店(5.0济南黄台环球家居店)</t>
+          <t>维也纳国际酒店(济南泉城欧乐堡传化店)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1850,14 +1850,14 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1867,7 +1867,7 @@
         <v>10</v>
       </c>
       <c r="M15" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="N15" t="n">
         <v>30</v>
@@ -1879,7 +1879,7 @@
         <v>30</v>
       </c>
       <c r="Q15" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="R15" t="n">
         <v>30</v>
@@ -1919,26 +1919,26 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>7114640050347837473</t>
+          <t>6601140134551226382</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（5.0版济南泉城欧乐堡传化店）</t>
+          <t>7天优品（济南大明湖店）</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(济南泉城欧乐堡传化店)</t>
+          <t>7天优品·济南大明湖店</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>10</v>
       </c>
       <c r="M16" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N16" t="n">
         <v>30</v>
@@ -2007,17 +2007,17 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>7628064337675946024</t>
+          <t>6775703716474537997</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（济南济阳九曲黄河万里情会展店）</t>
+          <t>希岸酒店（济南泉城欧乐堡中德产业园鑫茂店）</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(济南济阳九曲黄河万里情会展店)</t>
+          <t>希岸酒店(济南泉城欧乐堡店)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2026,36 +2026,36 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>搭门店,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L17" t="n">
         <v>10</v>
       </c>
       <c r="M17" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="N17" t="n">
         <v>30</v>
       </c>
       <c r="O17" t="n">
+        <v>30</v>
+      </c>
+      <c r="P17" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q17" t="n">
         <v>25</v>
-      </c>
-      <c r="P17" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>15</v>
       </c>
       <c r="R17" t="n">
         <v>30</v>
@@ -2095,22 +2095,22 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>6601140134551226382</t>
+          <t>6674104663681402894</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>7天优品（济南大明湖店）</t>
+          <t>维也纳酒店(济南火车站大明湖店)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>7天优品·济南大明湖店</t>
+          <t>维也纳酒店(济南火车站店)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H18" t="n">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -2131,7 +2131,7 @@
         <v>10</v>
       </c>
       <c r="M18" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N18" t="n">
         <v>30</v>
@@ -2143,7 +2143,7 @@
         <v>30</v>
       </c>
       <c r="Q18" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R18" t="n">
         <v>30</v>
@@ -2183,17 +2183,17 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>6775703716474537997</t>
+          <t>7058846272626624519</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>希岸酒店（济南泉城欧乐堡中德产业园鑫茂店）</t>
+          <t>维也纳酒店（5.0济南黄台环球家居店）</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>希岸酒店(济南泉城欧乐堡店)</t>
+          <t>维也纳酒店(5.0济南黄台环球家居店)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2205,11 +2205,11 @@
         <v>100</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K19" t="n">
@@ -2219,19 +2219,19 @@
         <v>10</v>
       </c>
       <c r="M19" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="N19" t="n">
         <v>30</v>
       </c>
       <c r="O19" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P19" t="n">
         <v>30</v>
       </c>
       <c r="Q19" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R19" t="n">
         <v>30</v>
@@ -2271,17 +2271,17 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>6674104663681402894</t>
+          <t>7628064337675946024</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>维也纳酒店(济南火车站大明湖店)</t>
+          <t>维也纳国际酒店（济南济阳九曲黄河万里情会展店）</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>维也纳酒店(济南火车站店)</t>
+          <t>维也纳国际酒店(济南济阳九曲黄河万里情会展店)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2290,18 +2290,18 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>搭门店,提质量,拿收益</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L20" t="n">
         <v>10</v>
@@ -2313,7 +2313,7 @@
         <v>30</v>
       </c>
       <c r="O20" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P20" t="n">
         <v>30</v>
@@ -2994,10 +2994,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -3023,7 +3023,7 @@
         <v>30</v>
       </c>
       <c r="Q28" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R28" t="n">
         <v>30</v>
